--- a/sampleprojects/CorporateTax/excel/states/DC_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/DC_corp.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="99">
   <si>
     <t>DT: Determine DC Filing Requirement</t>
   </si>
@@ -98,7 +98,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>// No nexus - no filing required; set apportionment.state_tax = 0.0; set result.dc_minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>// No nexus - no filing required; set apportionment.state_tax = 0.0; set dc_result.minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>DT: Calculate DC Income Adjustments</t>
@@ -149,13 +149,13 @@
     <t>DC flat rate calculation (8.25%)</t>
   </si>
   <si>
-    <t>// DC uses 8.25% flat rate; set apportionment.state_tax = apportionment.state_taxable_income * apportionment.state_tax_rate - apportionment.state_credits;</t>
+    <t>// DC uses 8.25% flat rate; set apportionment.state_tax = apportionment.state_taxable_income * dc_apportionment.state_tax_rate - apportionment.state_credits;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
   </si>
   <si>
-    <t>// No DC nexus - no tax liability; set apportionment.state_tax = 0.0; set result.dc_minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>// No DC nexus - no tax liability; set apportionment.state_tax = 0.0; set dc_result.minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>Nexus but no taxable income - minimum tax applies</t>
@@ -179,25 +179,25 @@
     <t>DC gross receipts exceed $1 million</t>
   </si>
   <si>
-    <t>result.dc_gross_receipts &gt; 1000000.0</t>
+    <t>dc_result.gross_receipts &gt; 1000000.0</t>
   </si>
   <si>
     <t>High gross receipts - $1,000 minimum</t>
   </si>
   <si>
-    <t>// Minimum tax: $1,000 for gross receipts &gt; $1M; set result.dc_minimum_tax = 1000.0; set apportionment.state_tax = max(apportionment.state_tax, result.dc_minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>// Minimum tax: $1,000 for gross receipts &gt; $1M; set dc_result.minimum_tax = 1000.0; set apportionment.state_tax = max(apportionment.state_tax, dc_result.minimum_tax); set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>Low gross receipts - $250 minimum</t>
   </si>
   <si>
-    <t>set result.dc_minimum_tax = 250.0; if apportionment.state_tax &gt; result.dc_minimum_tax then set apportionment.state_tax = apportionment.state_tax; else set apportionment.state_tax = result.dc_minimum_tax; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
+    <t>set dc_result.minimum_tax = 250.0; if apportionment.state_tax &gt; dc_result.minimum_tax then set apportionment.state_tax = apportionment.state_tax; else set apportionment.state_tax = dc_result.minimum_tax; endif set apportionment.state_refund_or_owed = apportionment.state_payments - apportionment.state_tax;</t>
   </si>
   <si>
     <t>No nexus - no minimum tax</t>
   </si>
   <si>
-    <t>// No DC nexus - no minimum tax requirement; set result.dc_minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
+    <t>// No DC nexus - no minimum tax requirement; set dc_result.minimum_tax = 0.0; set apportionment.state_refund_or_owed = apportionment.state_payments;</t>
   </si>
   <si>
     <t>EDD: EDD</t>
@@ -242,10 +242,10 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>apportionment</t>
-  </si>
-  <si>
-    <t>(8 attributes)</t>
+    <t>dc_apportionment</t>
+  </si>
+  <si>
+    <t>(4 attributes)</t>
   </si>
   <si>
     <t>apportionment_formula</t>
@@ -275,70 +275,43 @@
     <t>DC economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>state_additions</t>
+    <t>state_tax_rate</t>
+  </si>
+  <si>
+    <t>0.0825</t>
+  </si>
+  <si>
+    <t>DC corporate franchise tax rate: 8.25% flat rate (DC Code § 47-1807.02)</t>
+  </si>
+  <si>
+    <t>transaction_threshold</t>
+  </si>
+  <si>
+    <t>integer</t>
+  </si>
+  <si>
+    <t>200</t>
+  </si>
+  <si>
+    <t>DC economic nexus transaction count threshold: 200 transactions</t>
+  </si>
+  <si>
+    <t>dc_result</t>
+  </si>
+  <si>
+    <t>(2 attributes)</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
   </si>
   <si>
     <t>0.0</t>
   </si>
   <si>
-    <t>DC-specific additions: federal interest, IRC 199A addback, bonus depreciation, etc.</t>
-  </si>
-  <si>
-    <t>state_code</t>
-  </si>
-  <si>
-    <t>DC</t>
-  </si>
-  <si>
-    <t>District of Columbia code</t>
-  </si>
-  <si>
-    <t>state_credits</t>
-  </si>
-  <si>
-    <t>DC tax credits: R&amp;D, jobs, historic preservation, low-income housing, renewable energy, etc.</t>
-  </si>
-  <si>
-    <t>state_subtractions</t>
-  </si>
-  <si>
-    <t>DC-specific subtractions: DC municipal bond interest, state taxes, state NOL, etc.</t>
-  </si>
-  <si>
-    <t>state_tax_rate</t>
-  </si>
-  <si>
-    <t>0.0825</t>
-  </si>
-  <si>
-    <t>DC corporate franchise tax rate: 8.25% flat rate (DC Code § 47-1807.02)</t>
-  </si>
-  <si>
-    <t>transaction_threshold</t>
-  </si>
-  <si>
-    <t>integer</t>
-  </si>
-  <si>
-    <t>200</t>
-  </si>
-  <si>
-    <t>DC economic nexus transaction count threshold: 200 transactions</t>
-  </si>
-  <si>
-    <t>result</t>
-  </si>
-  <si>
-    <t>(2 attributes)</t>
-  </si>
-  <si>
-    <t>dc_gross_receipts</t>
-  </si>
-  <si>
     <t>DC gross receipts for minimum tax calculation</t>
   </si>
   <si>
-    <t>dc_minimum_tax</t>
+    <t>minimum_tax</t>
   </si>
   <si>
     <t>DC minimum franchise tax: $250 if receipts &lt;= $1M, $1000 if receipts &gt; $1M</t>
@@ -3185,14 +3158,14 @@
       <c r="B7" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C7" s="10" t="s">
-        <v>77</v>
+      <c r="C7" s="11" t="s">
+        <v>89</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F7" s="8" t="s">
         <v>14</v>
@@ -3201,7 +3174,7 @@
         <v>79</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I7" s="8" t="s">
         <v>14</v>
@@ -3220,267 +3193,103 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>91</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H8" s="16" t="s">
+      <c r="A8" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M8" s="7" t="s">
-        <v>14</v>
-      </c>
+      <c r="B8" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6"/>
+      <c r="L8" s="6"/>
+      <c r="M8" s="6"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C9" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="8" t="s">
+      <c r="D9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>79</v>
       </c>
       <c r="H9" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L9" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M9" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="J9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="M9" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="8" t="s">
         <v>14</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="D10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="8" t="s">
         <v>79</v>
       </c>
       <c r="H10" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M10" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B11" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>100</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H11" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="B12" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="C12" s="6"/>
-      <c r="D12" s="6"/>
-      <c r="E12" s="6"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6"/>
-      <c r="L12" s="6"/>
-      <c r="M12" s="6"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="M13" s="7" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="F14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>79</v>
-      </c>
-      <c r="H14" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="K14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>14</v>
-      </c>
-      <c r="M14" s="8" t="s">
+      <c r="I10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="M10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
